--- a/laporan_padel_dki_jakarta_2026-09-16.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-16.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.086.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.665.000</t>
+          <t>Rp3.915.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.595.000</t>
+          <t>Rp4.220.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>64</v>
       </c>
       <c r="D36" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.337.500</t>
+          <t>Rp2.482.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>144</v>
       </c>
       <c r="D59" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.689.000</t>
+          <t>Rp2.090.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>90</v>
       </c>
       <c r="D60" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp9.600.000</t>
+          <t>Rp9.900.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>72</v>
       </c>
       <c r="D71" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.070.000</t>
+          <t>Rp1.410.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>102</v>
       </c>
       <c r="D83" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>51</v>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp180.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.820.000</t>
+          <t>Rp5.360.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp4.775.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp5.975.000</t>
+          <t>Rp6.725.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp8.250.000</t>
+          <t>Rp7.500.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>144</v>
       </c>
       <c r="D58" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp57.000.000</t>
+          <t>Rp57.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.740.000</t>
+          <t>Rp13.320.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.000.000</t>
+          <t>Rp18.800.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>56</v>
       </c>
       <c r="D41" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>112</v>
       </c>
       <c r="D42" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp11.330.000</t>
+          <t>Rp10.780.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7909,16 +7909,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.185.000</t>
+          <t>Rp6.785.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.660.000</t>
+          <t>Rp4.005.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.125.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.960.000</t>
+          <t>Rp7.140.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp7.175.000</t>
+          <t>Rp6.675.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.180.000</t>
+          <t>Rp2.478.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-16.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-16.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp13.560.000</t>
+          <t>Rp14.420.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.926.981</t>
+          <t>Rp7.814.981</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.127.000</t>
+          <t>Rp10.558.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp16.150.000</t>
+          <t>Rp16.550.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>168</v>
       </c>
       <c r="D21" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.820.000</t>
+          <t>Rp18.095.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.915.000</t>
+          <t>Rp4.755.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1257,16 +1257,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp792.000</t>
+          <t>Rp1.190.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1288,16 +1288,16 @@
         <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.001.000</t>
+          <t>Rp1.251.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>64</v>
       </c>
       <c r="D30" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.016.000</t>
+          <t>Rp2.314.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>85</v>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.148.000</t>
+          <t>Rp3.344.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.530.000</t>
+          <t>Rp1.920.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>51</v>
       </c>
       <c r="D40" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.590.000</t>
+          <t>Rp2.815.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>60</v>
       </c>
       <c r="D43" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.738.000</t>
+          <t>Rp2.837.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp520.000</t>
+          <t>Rp628.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>68</v>
       </c>
       <c r="D61" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.840.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp5.553.000</t>
+          <t>Rp7.149.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>176</v>
       </c>
       <c r="D68" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.195.000</t>
+          <t>Rp2.191.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>72</v>
       </c>
       <c r="D71" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.410.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>96</v>
       </c>
       <c r="D73" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp3.660.000</t>
+          <t>Rp3.015.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>80</v>
       </c>
       <c r="D78" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>102</v>
       </c>
       <c r="D83" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>80</v>
       </c>
       <c r="D85" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp3.833.000</t>
+          <t>Rp4.231.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>138</v>
       </c>
       <c r="D86" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>90</v>
       </c>
       <c r="D87" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>112</v>
       </c>
       <c r="D88" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp5.420.000</t>
+          <t>Rp5.780.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>36</v>
       </c>
       <c r="D91" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp1.151.000</t>
+          <t>Rp1.269.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.256.000</t>
+          <t>Rp2.956.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.780.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.971.000</t>
+          <t>Rp5.371.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp9.875.000</t>
+          <t>Rp11.375.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.800.000</t>
+          <t>Rp9.360.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.775.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.499.000</t>
+          <t>Rp1.674.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp945.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.660.000</t>
+          <t>Rp3.360.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>60</v>
       </c>
       <c r="D28" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.935.000</t>
+          <t>Rp5.583.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp6.725.000</t>
+          <t>Rp7.275.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>68</v>
       </c>
       <c r="D57" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp9.720.000</t>
+          <t>Rp9.995.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>124</v>
       </c>
       <c r="D61" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>45</v>
       </c>
       <c r="D63" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.875.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp10.930.000</t>
+          <t>Rp11.630.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.940.000</t>
+          <t>Rp2.040.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp57.800.000</t>
+          <t>Rp59.250.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.775.000</t>
+          <t>Rp5.475.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.350.000</t>
+          <t>Rp6.530.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.045.000</t>
+          <t>Rp10.050.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.230.000</t>
+          <t>Rp5.360.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>85</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp8.250.000</t>
+          <t>Rp9.075.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.020.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp9.990.000</t>
+          <t>Rp10.440.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp10.058.000</t>
+          <t>Rp8.878.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp19.735.000</t>
+          <t>Rp19.905.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp891.000</t>
+          <t>Rp990.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp8.950.000</t>
+          <t>Rp9.440.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp24.100.000</t>
+          <t>Rp25.200.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp6.288.000</t>
+          <t>Rp6.476.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.565.000</t>
+          <t>Rp3.135.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp5.075.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>34</v>
       </c>
       <c r="D37" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.052.000</t>
+          <t>Rp1.628.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp29.000.000</t>
+          <t>Rp29.775.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>112</v>
       </c>
       <c r="D42" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp10.780.000</t>
+          <t>Rp11.055.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>174</v>
       </c>
       <c r="D43" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp31.600.000</t>
+          <t>Rp34.100.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>102</v>
       </c>
       <c r="D44" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp410.000</t>
+          <t>Rp860.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>144</v>
       </c>
       <c r="D48" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp1.240.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.605.000</t>
+          <t>Rp7.755.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.560.000</t>
+          <t>Rp5.635.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp135.000</t>
+          <t>Rp270.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.280.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp23.290.000</t>
+          <t>Rp25.250.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.675.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.175.000</t>
+          <t>Rp4.355.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.478.000</t>
+          <t>Rp3.073.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.132.000</t>
+          <t>Rp1.470.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp398.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-16.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-16.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.360.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.825.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.872.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp840.000</t>
+          <t>Rp1.592.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp8.450.000</t>
+          <t>Rp9.275.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.875.000</t>
+          <t>Rp5.375.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.814.981</t>
+          <t>Rp8.512.979</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.305.000</t>
+          <t>Rp9.505.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp4.900.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.350.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.755.000</t>
+          <t>Rp5.425.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp1.920.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>64</v>
       </c>
       <c r="D30" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.314.000</t>
+          <t>Rp2.890.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.490.000</t>
+          <t>Rp4.960.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.580.000</t>
+          <t>Rp3.072.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.220.000</t>
+          <t>Rp4.155.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>64</v>
       </c>
       <c r="D36" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.482.000</t>
+          <t>Rp2.907.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp3.330.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.920.000</t>
+          <t>Rp2.310.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>51</v>
       </c>
       <c r="D40" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.815.000</t>
+          <t>Rp3.060.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>60</v>
       </c>
       <c r="D43" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.837.000</t>
+          <t>Rp3.237.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>96</v>
       </c>
       <c r="D46" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp3.942.000</t>
+          <t>Rp4.192.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>64</v>
       </c>
       <c r="D50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.184.000</t>
+          <t>Rp6.912.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp628.000</t>
+          <t>Rp1.048.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>36</v>
       </c>
       <c r="D53" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>32</v>
       </c>
       <c r="D57" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp2.525.000</t>
+          <t>Rp4.075.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>36</v>
       </c>
       <c r="D58" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.588.000</t>
+          <t>Rp1.836.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>144</v>
       </c>
       <c r="D59" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.090.000</t>
+          <t>Rp2.488.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>30</v>
       </c>
       <c r="D62" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp99.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp7.149.000</t>
+          <t>Rp6.979.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.191.000</t>
+          <t>Rp2.291.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>90</v>
       </c>
       <c r="D72" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>96</v>
       </c>
       <c r="D73" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp3.015.000</t>
+          <t>Rp2.755.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2838,21 +2838,21 @@
         <v>80</v>
       </c>
       <c r="D78" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp100.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2993,16 +2993,16 @@
         <v>102</v>
       </c>
       <c r="D83" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>36</v>
       </c>
       <c r="D84" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp1.770.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>138</v>
       </c>
       <c r="D86" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp5.925.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>36</v>
       </c>
       <c r="D91" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp1.269.000</t>
+          <t>Rp1.567.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3478,16 +3478,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp648.000</t>
+          <t>Rp891.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.956.000</t>
+          <t>Rp6.612.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.450.000</t>
+          <t>Rp9.150.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp11.375.000</t>
+          <t>Rp11.875.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp590.000</t>
+          <t>Rp715.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp11.200.000</t>
+          <t>Rp10.300.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.650.000</t>
+          <t>Rp6.475.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.894.000</t>
+          <t>Rp2.243.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>60</v>
       </c>
       <c r="D28" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp5.583.000</t>
+          <t>Rp5.932.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.198.000</t>
+          <t>Rp1.298.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp7.275.000</t>
+          <t>Rp6.525.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>72</v>
       </c>
       <c r="D56" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp3.640.000</t>
+          <t>Rp3.440.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp53.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp10.350.000</t>
+          <t>Rp10.750.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp9.900.000</t>
+          <t>Rp8.700.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5730,16 +5730,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp19.140.000</t>
+          <t>Rp20.157.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.360.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp59.250.000</t>
+          <t>Rp59.500.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.360.000</t>
+          <t>Rp4.760.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.188.000</t>
+          <t>Rp1.416.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.040.000</t>
+          <t>Rp11.280.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6429,14 +6429,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp13.320.000</t>
+          <t>Rp13.900.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp12.000.000</t>
+          <t>Rp12.350.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.878.000</t>
+          <t>Rp9.586.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp19.905.000</t>
+          <t>Rp20.460.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.682.000</t>
+          <t>Rp6.177.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp7.890.000</t>
+          <t>Rp8.165.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.225.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.887.000</t>
+          <t>Rp5.694.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.800.000</t>
+          <t>Rp20.600.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.118.000</t>
+          <t>Rp7.716.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp5.945.000</t>
+          <t>Rp6.220.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp4.620.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.675.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.980.000</t>
+          <t>Rp4.120.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp9.440.000</t>
+          <t>Rp9.685.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp25.200.000</t>
+          <t>Rp25.900.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.075.000</t>
+          <t>Rp5.375.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>120</v>
       </c>
       <c r="D40" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp6.749.000</t>
+          <t>Rp7.549.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>112</v>
       </c>
       <c r="D42" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp11.055.000</t>
+          <t>Rp10.800.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>108</v>
       </c>
       <c r="D46" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>98</v>
       </c>
       <c r="D47" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp9.290.000</t>
+          <t>Rp8.950.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>144</v>
       </c>
       <c r="D48" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp1.880.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7940,16 +7940,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.080.000</t>
+          <t>Rp2.340.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp7.450.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.876.000</t>
+          <t>Rp7.146.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp270.000</t>
+          <t>Rp675.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp7.140.000</t>
+          <t>Rp6.555.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp5.975.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.355.000</t>
+          <t>Rp4.570.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp995.000</t>
+          <t>Rp1.430.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.576.000</t>
+          <t>Rp4.221.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.280.000</t>
+          <t>Rp5.920.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.675.000</t>
+          <t>Rp3.045.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.073.000</t>
+          <t>Rp3.172.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D41" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-16.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,28 +475,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fighter Hall</t>
+          <t>Budi Tester Sport Center</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>108</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.360.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rp60.000 - Rp100.000</t>
+          <t>Rp250.000</t>
         </is>
       </c>
     </row>
@@ -506,28 +506,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Homeground Padel Kedoya</t>
+          <t>Fighter Hall</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.825.000</t>
+          <t>Rp1.460.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp200.000</t>
+          <t>Rp60.000 - Rp100.000</t>
         </is>
       </c>
     </row>
@@ -537,28 +537,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Avion Sports Center</t>
+          <t>Homeground Padel Kedoya</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>144</v>
+        <v>68</v>
       </c>
       <c r="D4" t="n">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp14.420.000</t>
+          <t>Rp1.825.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rp180.000 - Rp1.000.000</t>
+          <t>Rp99.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -568,28 +568,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sunday Padel - Meruya</t>
+          <t>Avion Sports Center</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.872.000</t>
+          <t>Rp14.420.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp199.000</t>
+          <t>Rp180.000 - Rp1.000.000</t>
         </is>
       </c>
     </row>
@@ -599,28 +599,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Homeground Padel Premiere Kedoya</t>
+          <t>Sunday Padel - Meruya</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp3.872.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp250.000</t>
+          <t>Rp99.000 - Rp199.000</t>
         </is>
       </c>
     </row>
@@ -630,28 +630,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Orange Garden Padel Club</t>
+          <t>Homeground Padel Premiere Kedoya</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.592.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rp88.000 - Rp188.000</t>
+          <t>Rp150.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -661,28 +661,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Westside Padel</t>
+          <t>Orange Garden Padel Club</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp9.275.000</t>
+          <t>Rp1.592.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rp195.000 - Rp275.000</t>
+          <t>Rp88.000 - Rp188.000</t>
         </is>
       </c>
     </row>
@@ -692,28 +692,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Padel One Club</t>
+          <t>Westside Padel</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp5.375.000</t>
+          <t>Rp9.275.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp250.000</t>
+          <t>Rp195.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -723,28 +723,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EZ Padel Tomang</t>
+          <t>Padel One Club</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp8.512.979</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rp148.000 - Rp348.999</t>
+          <t>Rp150.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -754,28 +754,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Max Padel</t>
+          <t>EZ Padel Tomang</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp8.163.980</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp300.000</t>
+          <t>Rp148.000 - Rp348.999</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Citadel</t>
+          <t>Max Padel</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.505.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rp230.000 - Rp330.000</t>
+          <t>Rp125.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -816,28 +816,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Padel at largo - Kedoya</t>
+          <t>The Citadel</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp9.505.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp250.000</t>
+          <t>Rp230.000 - Rp330.000</t>
         </is>
       </c>
     </row>
@@ -847,28 +847,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vlocity Arena</t>
+          <t>Padel at largo - Kedoya</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>137</v>
+        <v>39</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.558.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rp78.000 - Rp330.000</t>
+          <t>Rp150.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -878,28 +878,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Boss Padel - Kedoya</t>
+          <t>Vlocity Arena</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp10.558.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp350.000</t>
+          <t>Rp78.000 - Rp330.000</t>
         </is>
       </c>
     </row>
@@ -909,28 +909,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Juego Padel Club (JPC)</t>
+          <t>Boss Padel - Kedoya</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.370.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp350.000</t>
+          <t>Rp100.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -940,28 +940,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stone Padel - Citra Garden City</t>
+          <t>Juego Padel Club (JPC)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp5.370.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp200.000</t>
+          <t>Rp80.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -971,28 +971,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daily Court</t>
+          <t>Stone Padel - Citra Garden City</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.975.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp210.000</t>
+          <t>Rp100.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1002,28 +1002,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>River Padel</t>
+          <t>Daily Court</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.021.000</t>
+          <t>Rp3.975.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp219.000</t>
+          <t>Rp100.000 - Rp210.000</t>
         </is>
       </c>
     </row>
@@ -1033,28 +1033,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KSC Racquet Club</t>
+          <t>River Padel</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp16.550.000</t>
+          <t>Rp3.021.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp305.000</t>
+          <t>Rp150.000 - Rp219.000</t>
         </is>
       </c>
     </row>
@@ -1064,28 +1064,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Anwa Racquet Privé (ex Anwa Tennis Club)</t>
+          <t>KSC Racquet Club</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.095.000</t>
+          <t>Rp16.550.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rp199.000 - Rp1.400.000</t>
+          <t>Rp150.000 - Rp305.000</t>
         </is>
       </c>
     </row>
@@ -1095,28 +1095,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Padel Spot</t>
+          <t>Anwa Racquet Privé (ex Anwa Tennis Club)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="D22" t="n">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp18.095.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp199.000 - Rp1.400.000</t>
         </is>
       </c>
     </row>
@@ -1126,23 +1126,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IPC Padel Club Kedoya</t>
+          <t>Padel Spot</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp4.900.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1157,28 +1157,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Badel Padel</t>
+          <t>IPC Padel Club Kedoya</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.425.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp295.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1188,28 +1188,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Base Padel</t>
+          <t>Badel Padel</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp5.425.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp225.000</t>
+          <t>Rp100.000 - Rp295.000</t>
         </is>
       </c>
     </row>
@@ -1219,28 +1219,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Patra Padel House</t>
+          <t>Base Padel</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp200.000</t>
+          <t>Rp150.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -1250,28 +1250,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Terra Padel Court</t>
+          <t>Patra Padel House</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D27" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.190.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp199.000</t>
+          <t>Rp125.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1281,28 +1281,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tinny Padel</t>
+          <t>Terra Padel Court</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.251.000</t>
+          <t>Rp1.190.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp188.000</t>
+          <t>Rp99.000 - Rp199.000</t>
         </is>
       </c>
     </row>
@@ -1312,28 +1312,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kobana Padel</t>
+          <t>Tinny Padel</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.920.000</t>
+          <t>Rp1.251.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp240.000</t>
+          <t>Rp125.000 - Rp188.000</t>
         </is>
       </c>
     </row>
@@ -1343,28 +1343,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Glass House Padel</t>
+          <t>Kobana Padel</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.890.000</t>
+          <t>Rp1.920.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rp90.000 - Rp288.000</t>
+          <t>Rp200.000 - Rp240.000</t>
         </is>
       </c>
     </row>
@@ -1374,28 +1374,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sini Padel Court</t>
+          <t>Glass House Padel</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.344.000</t>
+          <t>Rp2.890.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rp98.000 - Rp200.000</t>
+          <t>Rp90.000 - Rp288.000</t>
         </is>
       </c>
     </row>
@@ -1405,28 +1405,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Xcite Padel</t>
+          <t>Sini Padel Court</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D32" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp4.960.000</t>
+          <t>Rp3.344.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp230.000</t>
+          <t>Rp98.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1436,28 +1436,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hobi Padel Meruya</t>
+          <t>Xcite Padel</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D33" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.072.000</t>
+          <t>Rp4.960.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rp98.000 - Rp148.000</t>
+          <t>Rp125.000 - Rp230.000</t>
         </is>
       </c>
     </row>
@@ -1467,28 +1467,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Padel Point</t>
+          <t>Hobi Padel Meruya</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D34" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.072.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp250.000</t>
+          <t>Rp98.000 - Rp148.000</t>
         </is>
       </c>
     </row>
@@ -1498,28 +1498,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RacketGo Citra 5</t>
+          <t>The Padel Point</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D35" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.155.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp190.000</t>
+          <t>Rp150.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -1529,28 +1529,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Eagle Padel PIK</t>
+          <t>RacketGo Citra 5</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.907.000</t>
+          <t>Rp4.155.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rp144.500 - Rp212.500</t>
+          <t>Rp125.000 - Rp190.000</t>
         </is>
       </c>
     </row>
@@ -1560,28 +1560,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>La Chiquita Padel</t>
+          <t>Eagle Padel PIK</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="D37" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp2.907.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp300.000</t>
+          <t>Rp144.500 - Rp212.500</t>
         </is>
       </c>
     </row>
@@ -1591,28 +1591,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Padre Padel Duri Kosambi</t>
+          <t>La Chiquita Padel</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="D38" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.330.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp210.000</t>
+          <t>Rp200.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Padeloo</t>
+          <t>Padre Padel Duri Kosambi</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.310.000</t>
+          <t>Rp3.690.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp195.000</t>
+          <t>Rp150.000 - Rp210.000</t>
         </is>
       </c>
     </row>
@@ -1653,28 +1653,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CPH Citra Padel House</t>
+          <t>Padeloo</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp3.060.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp170.000</t>
+          <t>Rp99.000 - Rp195.000</t>
         </is>
       </c>
     </row>
@@ -1684,28 +1684,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vamos Arena Indonesia</t>
+          <t>CPH Citra Padel House</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="D41" t="n">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp7.400.000</t>
+          <t>Rp3.060.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp400.000</t>
+          <t>Rp75.000 - Rp170.000</t>
         </is>
       </c>
     </row>
@@ -1715,28 +1715,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Level 9 Padel</t>
+          <t>Vamos Arena Indonesia</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="D42" t="n">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp7.400.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp150.000</t>
+          <t>Rp200.000 - Rp400.000</t>
         </is>
       </c>
     </row>
@@ -1746,28 +1746,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Como Padel Court</t>
+          <t>The Level 9 Padel</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>60</v>
+        <v>198</v>
       </c>
       <c r="D43" t="n">
-        <v>42</v>
+        <v>175</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.237.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp200.000</t>
+          <t>Rp125.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -1777,28 +1777,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>World Padel</t>
+          <t>Como Padel Court</t>
         </is>
       </c>
       <c r="C44" t="n">
+        <v>60</v>
+      </c>
+      <c r="D44" t="n">
         <v>42</v>
       </c>
-      <c r="D44" t="n">
-        <v>24</v>
-      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.875.000</t>
+          <t>Rp3.237.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp225.000</t>
+          <t>Rp99.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1808,28 +1808,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Padelin</t>
+          <t>World Padel</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D45" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.180.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp200.000</t>
+          <t>Rp50.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -1839,28 +1839,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nordic Courts</t>
+          <t>Padelin</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="D46" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp4.192.000</t>
+          <t>Rp1.180.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rp77.000 - Rp250.000</t>
+          <t>Rp70.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1870,28 +1870,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Courtyard Padel Club</t>
+          <t>Nordic Courts</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D47" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp7.555.000</t>
+          <t>Rp4.192.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rp165.000 - Rp590.000</t>
+          <t>Rp77.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -1901,28 +1901,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Padel On Mars</t>
+          <t>Courtyard Padel Club</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="D48" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp7.555.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rp115.000 - Rp135.000</t>
+          <t>Rp165.000 - Rp590.000</t>
         </is>
       </c>
     </row>
@@ -1932,28 +1932,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Padel Meruya Airdome</t>
+          <t>Padel On Mars</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="D49" t="n">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.192.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rp349.000 - Rp399.000</t>
+          <t>Rp115.000 - Rp135.000</t>
         </is>
       </c>
     </row>
@@ -1963,28 +1963,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hachi Padel Puri Indah Jakarta</t>
+          <t>Padel Meruya Airdome</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D50" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp6.912.000</t>
+          <t>Rp3.192.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rp288.000</t>
+          <t>Rp349.000 - Rp399.000</t>
         </is>
       </c>
     </row>
@@ -1994,28 +1994,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JC Padel Kedoya</t>
+          <t>Hachi Padel Puri Indah Jakarta</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp1.180.000</t>
+          <t>Rp6.912.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp380.000</t>
+          <t>Rp288.000</t>
         </is>
       </c>
     </row>
@@ -2025,28 +2025,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tennis Padel Matic Mal Ciputra</t>
+          <t>JC Padel Kedoya</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D52" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.048.000</t>
+          <t>Rp1.180.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rp96.000 - Rp140.000</t>
+          <t>Rp100.000 - Rp380.000</t>
         </is>
       </c>
     </row>
@@ -2056,28 +2056,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Paddle Padel</t>
+          <t>Tennis Padel Matic Mal Ciputra</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.048.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp96.000 - Rp140.000</t>
         </is>
       </c>
     </row>
@@ -2087,28 +2087,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Roots Padel House</t>
+          <t>Paddle Padel</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D54" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp549.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rp149.000 - Rp200.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2118,28 +2118,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Coco Padel Court Jakarta</t>
+          <t>Roots Padel House</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.745.000</t>
+          <t>Rp549.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp200.000</t>
+          <t>Rp149.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2149,28 +2149,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Zplay Padel</t>
+          <t>Coco Padel Court Jakarta</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.835.000</t>
+          <t>Rp2.145.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rp65.000 - Rp175.000</t>
+          <t>Rp100.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2180,28 +2180,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PPC - Puri Padel Club</t>
+          <t>Zplay Padel</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D57" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp4.075.000</t>
+          <t>Rp1.835.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rp225.000 - Rp275.000</t>
+          <t>Rp65.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -2211,28 +2211,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Donkey Padel</t>
+          <t>PPC - Puri Padel Club</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.836.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp149.000</t>
+          <t>Rp225.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -2242,28 +2242,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sunrise Padel - Sunrise Garden</t>
+          <t>Donkey Padel</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.488.000</t>
+          <t>Rp1.836.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp199.000</t>
+          <t>Rp99.000 - Rp149.000</t>
         </is>
       </c>
     </row>
@@ -2273,28 +2273,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ace Padel Club (APC) - Jalan Panjang Kedoya</t>
+          <t>Sunrise Padel - Sunrise Garden</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="D60" t="n">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp9.900.000</t>
+          <t>Rp2.488.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp300.000</t>
+          <t>Rp100.000 - Rp199.000</t>
         </is>
       </c>
     </row>
@@ -2304,28 +2304,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Padel Quarter</t>
+          <t>Ace Padel Club (APC) - Jalan Panjang Kedoya</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D61" t="n">
         <v>49</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp9.900.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp380.000</t>
+          <t>Rp100.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -2335,28 +2335,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ZEN PADEL</t>
+          <t>Padel Quarter</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp3.640.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rp59.000 - Rp99.000</t>
+          <t>Rp80.000 - Rp380.000</t>
         </is>
       </c>
     </row>
@@ -2366,28 +2366,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Go 2 Padel</t>
+          <t>ZEN PADEL</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D63" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp99.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rp60.000 - Rp150.000</t>
+          <t>Rp59.000 - Rp99.000</t>
         </is>
       </c>
     </row>
@@ -2397,28 +2397,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YOLO Padel and Lifestyle Slipi</t>
+          <t>Go 2 Padel</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rp300.000 - Rp375.000</t>
+          <t>Rp60.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -2428,28 +2428,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KALMA Social Club - Jl. Panjang, Kedoya</t>
+          <t>YOLO Padel and Lifestyle Slipi</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="D65" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp6.979.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp399.000</t>
+          <t>Rp300.000 - Rp375.000</t>
         </is>
       </c>
     </row>
@@ -2459,28 +2459,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Padel V</t>
+          <t>KALMA Social Club - Jl. Panjang, Kedoya</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp6.979.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rp160.000 - Rp260.000</t>
+          <t>Rp150.000 - Rp399.000</t>
         </is>
       </c>
     </row>
@@ -2490,28 +2490,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Country Club | Padel &amp; Lounge</t>
+          <t>Padel V</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D67" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp250.000</t>
+          <t>Rp160.000 - Rp260.000</t>
         </is>
       </c>
     </row>
@@ -2521,28 +2521,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Social Field</t>
+          <t>Country Club | Padel &amp; Lounge</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>176</v>
+        <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.291.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rp99.500 - Rp299.000</t>
+          <t>Rp200.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -2552,28 +2552,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PIPC - Play In Padel Collective - Srengseng</t>
+          <t>Social Field</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp5.425.000</t>
+          <t>Rp2.291.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp250.000</t>
+          <t>Rp99.500 - Rp299.000</t>
         </is>
       </c>
     </row>
@@ -2583,28 +2583,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>United Padel Club</t>
+          <t>PIPC - Play In Padel Collective - Srengseng</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.080.000</t>
+          <t>Rp5.425.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rp120.000 - Rp180.000</t>
+          <t>Rp100.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -2614,28 +2614,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Powerhouse Padel AZURE Taman Surya</t>
+          <t>United Padel Club</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D71" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp170.000</t>
+          <t>Rp120.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -2645,28 +2645,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kore Padel</t>
+          <t>Powerhouse Padel AZURE Taman Surya</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp325.000</t>
+          <t>Rp75.000 - Rp170.000</t>
         </is>
       </c>
     </row>
@@ -2676,28 +2676,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OLA PADEL CLUB</t>
+          <t>Kore Padel</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp2.755.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp260.000</t>
+          <t>Rp200.000 - Rp325.000</t>
         </is>
       </c>
     </row>
@@ -2707,28 +2707,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MMT Padel</t>
+          <t>OLA PADEL CLUB</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp2.755.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rp230.000 - Rp350.000</t>
+          <t>Rp100.000 - Rp260.000</t>
         </is>
       </c>
     </row>
@@ -2738,28 +2738,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Clubhouse Meruya</t>
+          <t>MMT Padel</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D75" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.740.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rp195.000 - Rp245.000</t>
+          <t>Rp230.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -2769,28 +2769,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Angke Padel</t>
+          <t>Clubhouse Meruya</t>
         </is>
       </c>
       <c r="C76" t="n">
+        <v>120</v>
+      </c>
+      <c r="D76" t="n">
         <v>108</v>
       </c>
-      <c r="D76" t="n">
-        <v>92</v>
-      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.175.000</t>
+          <t>Rp2.740.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp150.000</t>
+          <t>Rp195.000 - Rp245.000</t>
         </is>
       </c>
     </row>
@@ -2800,28 +2800,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DAAN MOGOT PADEL COURT</t>
+          <t>Angke Padel</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D77" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp850.000</t>
+          <t>Rp2.175.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp500.000</t>
+          <t>Rp75.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -2831,28 +2831,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Kaia Padel Reserve</t>
+          <t>DAAN MOGOT PADEL COURT</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D78" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp850.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp200.000</t>
+          <t>Rp125.000 - Rp500.000</t>
         </is>
       </c>
     </row>
@@ -2862,28 +2862,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tangkas Padel</t>
+          <t>Kaia Padel Reserve</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="D79" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp300.000</t>
+          <t>Rp100.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2893,28 +2893,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cosmo Padel</t>
+          <t>Tangkas Padel</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D80" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp275.000</t>
+          <t>Rp150.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -2924,28 +2924,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MAISON de PADEL</t>
+          <t>Cosmo Padel</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D81" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rp275.000 - Rp450.000</t>
+          <t>Rp100.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -2955,28 +2955,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Di Atas Social Club - Lippo Mall Puri</t>
+          <t>MAISON de PADEL</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="D82" t="n">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rp195.000 - Rp280.000</t>
+          <t>Rp275.000 - Rp450.000</t>
         </is>
       </c>
     </row>
@@ -2986,28 +2986,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Commune Courts</t>
+          <t>Di Atas Social Club - Lippo Mall Puri</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="D83" t="n">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp6.700.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp300.000</t>
+          <t>Rp195.000 - Rp280.000</t>
         </is>
       </c>
     </row>
@@ -3017,28 +3017,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EL WILLY PADEL</t>
+          <t>Commune Courts</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D84" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp380.000</t>
+          <t>Rp100.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -3048,28 +3048,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dash Padel House</t>
+          <t>EL WILLY PADEL</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="D85" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp4.231.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp249.000</t>
+          <t>Rp250.000 - Rp380.000</t>
         </is>
       </c>
     </row>
@@ -3079,28 +3079,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Citra Padel Club</t>
+          <t>Dash Padel House</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="D86" t="n">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.925.000</t>
+          <t>Rp4.231.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp225.000</t>
+          <t>Rp100.000 - Rp249.000</t>
         </is>
       </c>
     </row>
@@ -3110,28 +3110,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Malta Padel Club</t>
+          <t>Citra Padel Club</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="D87" t="n">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.925.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp70.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -3141,28 +3141,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>De Luz Padel</t>
+          <t>Malta Padel Club</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="D88" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp5.780.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp180.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -3172,28 +3172,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dale Padel</t>
+          <t>De Luz Padel</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="D89" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp5.780.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp165.000</t>
+          <t>Rp80.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -3203,28 +3203,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nice Padel</t>
+          <t>Dale Padel</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D90" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp50.000 - Rp165.000</t>
         </is>
       </c>
     </row>
@@ -3234,28 +3234,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Golcindo Padel Club</t>
+          <t>Nice Padel</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D91" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp1.567.000</t>
+          <t>Rp594.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rp59.000 - Rp149.000</t>
+          <t>Rp99.000</t>
         </is>
       </c>
     </row>
@@ -3265,28 +3265,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mono House</t>
+          <t>Golcindo Padel Club</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D92" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp1.567.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp225.000</t>
+          <t>Rp59.000 - Rp149.000</t>
         </is>
       </c>
     </row>
@@ -3296,28 +3296,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Seven Stars Arena</t>
+          <t>Mono House</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D93" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp2.010.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp220.000</t>
+          <t>Rp125.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -3327,28 +3327,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deuce Arena</t>
+          <t>Seven Stars Arena</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="D94" t="n">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp4.360.000</t>
+          <t>Rp2.010.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp250.000</t>
+          <t>Rp125.000 - Rp220.000</t>
         </is>
       </c>
     </row>
@@ -3358,28 +3358,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Alley Social Padel Mahjong By Homeground</t>
+          <t>Deuce Arena</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="D95" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp3.190.000</t>
+          <t>Rp4.480.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp225.000</t>
+          <t>Rp70.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -3389,26 +3389,57 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>Alley Social Padel Mahjong By Homeground</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>68</v>
+      </c>
+      <c r="D96" t="n">
+        <v>52</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Rp3.190.000</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Rp75.000 - Rp225.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>SERA COMMUNITY CLUB</t>
         </is>
       </c>
-      <c r="C96" t="n">
+      <c r="C97" t="n">
         <v>28</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D97" t="n">
         <v>22</v>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>21.4%</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Rp1.930.000</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Rp165.000 - Rp400.000</t>
         </is>
@@ -3540,16 +3571,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp6.612.000</t>
+          <t>Rp8.168.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3571,16 +3602,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.150.000</t>
+          <t>Rp8.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3633,16 +3664,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.360.000</t>
+          <t>Rp5.710.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4408,16 +4439,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.298.000</t>
+          <t>Rp1.698.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4656,16 +4687,16 @@
         <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp6.525.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4873,16 +4904,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5183,16 +5214,16 @@
         <v>68</v>
       </c>
       <c r="D57" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp9.995.000</t>
+          <t>Rp10.270.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5730,16 +5761,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp20.157.500</t>
+          <t>Rp20.817.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5792,16 +5823,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.400.000</t>
+          <t>Rp9.650.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6133,16 +6164,16 @@
         <v>85</v>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp9.075.000</t>
+          <t>Rp10.175.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6432,16 +6463,16 @@
         <v>79</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp237.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6463,16 +6494,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp13.900.000</t>
+          <t>Rp14.400.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6680,16 +6711,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.177.000</t>
+          <t>Rp6.775.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6897,16 +6928,16 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp990.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7052,16 +7083,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.220.000</t>
+          <t>Rp6.495.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7300,16 +7331,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp25.900.000</t>
+          <t>Rp26.300.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7672,16 +7703,16 @@
         <v>36</v>
       </c>
       <c r="D45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp6.690.000</t>
+          <t>Rp6.940.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8002,16 +8033,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.135.000</t>
+          <t>Rp3.537.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8498,16 +8529,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp320.000</t>
+          <t>Rp480.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8529,16 +8560,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.835.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8622,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.975.000</t>
+          <t>Rp5.725.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8715,16 +8746,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8839,16 +8870,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.080.000</t>
+          <t>Rp2.660.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -8901,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.035.000</t>
+          <t>Rp3.615.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9025,16 +9056,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.650.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-16.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-16.xlsx
@@ -606,16 +606,16 @@
         <v>80</v>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.872.000</t>
+          <t>Rp4.270.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp8.163.980</t>
+          <t>Rp7.867.980</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>180</v>
       </c>
       <c r="D15" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp10.558.000</t>
+          <t>Rp10.480.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.975.000</t>
+          <t>Rp4.075.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp549.000</t>
+          <t>Rp698.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.425.000</t>
+          <t>Rp5.525.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>108</v>
       </c>
       <c r="D77" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp2.175.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp4.480.000</t>
+          <t>Rp4.730.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>119</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.175.420</t>
+          <t>Rp14.350.420</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.200.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>170</v>
       </c>
       <c r="D29" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp15.570.000</t>
+          <t>Rp15.845.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.698.000</t>
+          <t>Rp1.898.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp20.817.500</t>
+          <t>Rp20.597.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.530.000</t>
+          <t>Rp6.030.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.409.000</t>
+          <t>Rp2.607.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>85</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp10.175.000</t>
+          <t>Rp10.450.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp9.300.000</t>
+          <t>Rp11.000.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>79</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp237.000</t>
+          <t>Rp573.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp14.400.000</t>
+          <t>Rp14.595.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.275.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.586.000</t>
+          <t>Rp10.086.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp20.460.000</t>
+          <t>Rp20.696.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.135.000</t>
+          <t>Rp3.334.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp29.775.000</t>
+          <t>Rp30.000.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp670.000</t>
+          <t>Rp970.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.625.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.725.000</t>
+          <t>Rp5.975.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp5.300.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
